--- a/maps/map1_без_направлений.xlsx
+++ b/maps/map1_без_направлений.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D553F836-C3EF-4C96-B9FE-154EDA9E8548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFBA121-899D-4F47-B7CA-C1F8E8F70DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
